--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -808,670 +808,682 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9919,0.0012,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.0089,0.0001,0.0000,0.9979</t>
-  </si>
-  <si>
-    <t>0.9845,0.0001,0.0001,0.0120</t>
-  </si>
-  <si>
-    <t>0.0588,0.0030,0.0001,0.9645</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9966,0.0003,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0000,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0308,0.0010,0.0010,0.9858</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9417,0.0003,0.0697,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0040,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.6527,0.0001,0.5502,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0007,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.9875,0.0003,0.0139,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4324,0.7673,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7785,0.0035,0.2035,0.0005</t>
+  </si>
+  <si>
+    <t>0.2534,0.0014,0.7392,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.0005,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0111,0.0010,0.9829,0.0005</t>
+  </si>
+  <si>
+    <t>0.3678,0.0000,0.7865,0.0000</t>
+  </si>
+  <si>
+    <t>0.4059,0.0001,0.7361,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.1614,0.8953,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.1065,0.1180,0.4956,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9997,0.0033</t>
+  </si>
+  <si>
+    <t>0.0011,0.9977,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9930,0.0010,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0007,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.1263,0.8757,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9947,0.0524,0.0002</t>
+  </si>
+  <si>
+    <t>0.0482,0.7458,0.0502,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0020,0.9939,0.0004</t>
+  </si>
+  <si>
+    <t>0.0056,0.0002,0.9907,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9976,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0053,0.9998,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9269,0.0004,0.8858</t>
+  </si>
+  <si>
+    <t>0.0006,0.9991,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0029,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0394,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0125,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9978,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0402,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,0.9999,0.0073</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0002,0.0000</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.0000,0.9786,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0038,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9988,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.9962,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0036,0.0000</t>
+  </si>
+  <si>
+    <t>0.8772,0.0023,0.1346,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.0029,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9767,0.9729,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.4646,0.9613,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.4564,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0016,0.9997</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0022,0.0001,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.5014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9589,0.9316,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9116,0.9782,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.1271,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0031,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9670,0.0021,0.0169,0.0002</t>
-  </si>
-  <si>
-    <t>0.1549,0.0024,0.8332,0.0004</t>
-  </si>
-  <si>
-    <t>0.9645,0.0004,0.0456,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0003,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.6444,0.0001,0.5601,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9990,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9861,0.0001,0.0085,0.0001</t>
-  </si>
-  <si>
-    <t>0.1885,0.0008,0.6830,0.0092</t>
-  </si>
-  <si>
-    <t>0.0064,0.0001,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0062,0.0006,0.9901,0.0003</t>
-  </si>
-  <si>
-    <t>0.1062,0.0000,0.9431,0.0000</t>
-  </si>
-  <si>
-    <t>0.8193,0.0000,0.2729,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0004,0.9966,0.0025</t>
-  </si>
-  <si>
-    <t>0.1039,0.9416,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.3529,0.7307,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0381,0.9992,0.0147</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9922,0.0004,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.5687,0.0002,0.5658,0.0006</t>
-  </si>
-  <si>
-    <t>0.2865,0.7316,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9955,0.0520,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.9737,0.0141,0.0006</t>
-  </si>
-  <si>
-    <t>0.0017,0.0019,0.9932,0.0009</t>
-  </si>
-  <si>
-    <t>0.0053,0.0114,0.9875,0.0003</t>
-  </si>
-  <si>
-    <t>0.0942,0.0001,0.8960,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.1267,0.9949,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.9996,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.1256,0.0243,0.9167</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1489,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0107,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0001,0.9934,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0078,0.9987,0.0012</t>
-  </si>
-  <si>
-    <t>0.9912,0.0108,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0024,0.9992,0.0055</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9862,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0737,0.9985,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.0056,0.9973,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9984,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9103,0.0003,0.1406,0.0002</t>
-  </si>
-  <si>
-    <t>0.9838,0.0063,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.8985,0.9827,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.4881,0.9801,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9942,0.7912,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0009,0.9996</t>
+    <t>0.0000,0.0000,0.9999,0.0045</t>
+  </si>
+  <si>
+    <t>0.0167,0.0007,0.9806,0.0001</t>
+  </si>
+  <si>
+    <t>0.3574,0.0002,0.6608,0.0015</t>
+  </si>
+  <si>
+    <t>0.9549,0.0002,0.0602,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9996,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9959,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9977,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3067,0.7515,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.3810,0.0066,0.4301,0.0021</t>
+  </si>
+  <si>
+    <t>0.0858,0.0011,0.9182,0.0001</t>
+  </si>
+  <si>
+    <t>0.7180,0.0315,0.0449,0.0086</t>
+  </si>
+  <si>
+    <t>0.4833,0.0068,0.3099,0.0018</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.0006,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0790,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9344,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9989,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.5643,0.1860,0.0449,0.0000</t>
+  </si>
+  <si>
+    <t>0.9399,0.0727,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0045,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.7525,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0792,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0009,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0590,0.0025,0.9444,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0001,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.2684,0.0002,0.7867,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0007,0.9930,0.0030</t>
+  </si>
+  <si>
+    <t>0.9697,0.0005,0.0147,0.0002</t>
+  </si>
+  <si>
+    <t>0.0686,0.0001,0.0001,0.9827</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.9898,0.2125,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9911,0.9621,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.8416,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.6757,0.9600,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9876,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9944,0.9307,0.0000</t>
+    <t>0.0004,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9957,0.9901,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9983,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.0237,0.9736,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.8401,0.0000,0.0002,0.3805</t>
+  </si>
+  <si>
+    <t>0.0008,0.0043,0.9970,0.0067</t>
+  </si>
+  <si>
+    <t>0.9661,0.0000,0.0138,0.0015</t>
+  </si>
+  <si>
+    <t>0.1593,0.8462,0.0064,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0438,0.9050,0.0342,0.0002</t>
+  </si>
+  <si>
+    <t>0.9884,0.0029,0.0035,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9791,0.0061,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9467,0.0397,0.0054,0.0003</t>
+  </si>
+  <si>
+    <t>0.9208,0.1261,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1501,0.0050,0.9096,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0008,0.0009</t>
   </si>
   <si>
     <t>0.9994,0.0004,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0010</t>
-  </si>
-  <si>
-    <t>0.0016,0.0046,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.8970,0.0000,0.1117,0.0003</t>
-  </si>
-  <si>
-    <t>0.0095,0.0006,0.9936,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.9935,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1880,0.8640,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.1924,0.0105,0.5896,0.0083</t>
-  </si>
-  <si>
-    <t>0.7116,0.0002,0.3484,0.0002</t>
-  </si>
-  <si>
-    <t>0.2692,0.2903,0.0360,0.0155</t>
-  </si>
-  <si>
-    <t>0.8746,0.0207,0.0261,0.0018</t>
-  </si>
-  <si>
-    <t>0.0004,0.0295,0.0002,0.9983</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.9250,0.0240,0.0184,0.0001</t>
-  </si>
-  <si>
-    <t>0.2719,0.7350,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.8289,0.9934,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.1447,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0042,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0470,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0212,0.0010,0.9715,0.0004</t>
-  </si>
-  <si>
-    <t>0.0174,0.0001,0.9868,0.0002</t>
-  </si>
-  <si>
-    <t>0.9912,0.0002,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.0390,0.0000,0.0000,0.9928</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9933,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.9895,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.0076,0.9912,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0000,0.0001,0.0044</t>
-  </si>
-  <si>
-    <t>0.0004,0.0029,0.9981,0.0103</t>
-  </si>
-  <si>
-    <t>0.8721,0.0000,0.0035,0.0158</t>
-  </si>
-  <si>
-    <t>0.0527,0.9643,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0005,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.8780,0.0238,0.0385,0.0001</t>
-  </si>
-  <si>
-    <t>0.9907,0.0043,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9816,0.0110,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9821,0.0092,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.7483,0.2196,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.9632,0.0573,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.1181,0.1325,0.7219,0.0055</t>
-  </si>
-  <si>
-    <t>0.9990,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0014,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9851,0.0140,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9909,0.0080,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0481,0.9990,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0047,0.0044,0.9894,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.0062,0.0032,0.9874,0.0007</t>
-  </si>
-  <si>
-    <t>0.1080,0.0059,0.8177,0.0004</t>
-  </si>
-  <si>
-    <t>0.5801,0.1188,0.0693,0.0001</t>
-  </si>
-  <si>
-    <t>0.0069,0.0542,0.9588,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.0009,0.9852,0.0001</t>
-  </si>
-  <si>
-    <t>0.5054,0.0007,0.3989,0.0031</t>
-  </si>
-  <si>
-    <t>0.0049,0.0024,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.0361,0.9724,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0498,0.9747,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9215,0.1517,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8754,0.2070,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0661,0.9551,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9520,0.0198,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9863,0.0005,0.0046,0.0003</t>
-  </si>
-  <si>
-    <t>0.6629,0.0056,0.2898,0.0009</t>
-  </si>
-  <si>
-    <t>0.2296,0.0114,0.6546,0.0020</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9977,0.0016</t>
-  </si>
-  <si>
-    <t>0.0052,0.0049,0.9754,0.0045</t>
-  </si>
-  <si>
-    <t>0.0069,0.1245,0.9577,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0095,0.0311,0.9139,0.0011</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0012,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0011,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0010</t>
-  </si>
-  <si>
-    <t>0.0784,0.0085,0.8871,0.0008</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0197,0.0000,0.9869,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0032,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0526,0.9967,0.0011</t>
+    <t>0.9928,0.0057,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0034,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.6818,0.2186,0.0234,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0247,0.9995,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0280,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0019,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.0007,0.9952,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.0014,0.9919,0.0001</t>
+  </si>
+  <si>
+    <t>0.0177,0.0034,0.9757,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0604,0.9752,0.0001</t>
+  </si>
+  <si>
+    <t>0.4637,0.0005,0.6578,0.0000</t>
+  </si>
+  <si>
+    <t>0.9579,0.0002,0.0430,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.0008,0.9929,0.0008</t>
+  </si>
+  <si>
+    <t>0.0919,0.9353,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0512,0.9738,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8965,0.2294,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1474,0.9075,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9131,0.1324,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8513,0.0920,0.0045,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9874,0.0009,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.1625,0.0155,0.6659,0.0031</t>
+  </si>
+  <si>
+    <t>0.0316,0.0033,0.9480,0.0066</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.9948,0.0014</t>
+  </si>
+  <si>
+    <t>0.0025,0.0071,0.9904,0.0009</t>
+  </si>
+  <si>
+    <t>0.0144,0.0226,0.9701,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.0188,0.9769,0.0008</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0014,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9996,0.0013</t>
+  </si>
+  <si>
+    <t>0.0069,0.0667,0.9582,0.0014</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0096,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.6647,0.9852,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0131,0.0004,0.9856,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0081,0.0217,0.9701,0.0027</t>
-  </si>
-  <si>
-    <t>0.1773,0.0104,0.7204,0.0010</t>
-  </si>
-  <si>
-    <t>0.9898,0.0000,0.0111,0.0000</t>
-  </si>
-  <si>
-    <t>0.9901,0.0002,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0254,0.0457,0.8591,0.0002</t>
-  </si>
-  <si>
-    <t>0.0144,0.0001,0.9866,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9937,0.0381</t>
-  </si>
-  <si>
-    <t>0.0021,0.0006,0.9949,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.0009,0.9914,0.0023</t>
-  </si>
-  <si>
-    <t>0.9933,0.0000,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0074,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.1781,0.0000,0.0003,0.9238</t>
+    <t>0.0095,0.0011,0.9857,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0089,0.9961,0.0009</t>
+  </si>
+  <si>
+    <t>0.9846,0.0006,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.9516,0.0000,0.0749,0.0000</t>
+  </si>
+  <si>
+    <t>0.9902,0.0000,0.0108,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0032,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0431,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0063,0.9877,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0011,0.9920,0.0218</t>
+  </si>
+  <si>
+    <t>0.0161,0.0051,0.9690,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9972,0.0024</t>
+  </si>
+  <si>
+    <t>0.9832,0.0001,0.0008,0.0081</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0088,0.0000,0.0028,0.9905</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9966,0.0001,0.0000,0.0013</t>
+    <t>0.9964,0.0002,0.0001,0.0009</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1871,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1885,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1899,7 +1911,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1913,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1927,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1941,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1955,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1969,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1983,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1997,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2011,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2025,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2039,7 +2051,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2050,10 +2062,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2067,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2078,10 +2090,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2095,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2109,7 +2121,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2123,7 +2135,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2137,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2151,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2165,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2179,7 +2191,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2193,7 +2205,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2207,7 +2219,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2221,7 +2233,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2232,10 +2244,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2249,7 +2261,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2263,7 +2275,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,10 +2286,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2291,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2305,7 +2317,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2319,7 +2331,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2330,10 +2342,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2347,7 +2359,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2361,7 +2373,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,7 +2387,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2389,7 +2401,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2403,7 +2415,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,7 +2429,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2431,7 +2443,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2445,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2459,7 +2471,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,10 +2482,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2487,7 +2499,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2501,7 +2513,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2515,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2529,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2543,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2557,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2571,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2585,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2599,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2613,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2627,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2641,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2655,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2669,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2683,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2697,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2711,7 +2723,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2725,7 +2737,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2739,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2753,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2767,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2781,7 +2793,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2795,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2809,7 +2821,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2823,7 +2835,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2837,7 +2849,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2851,7 +2863,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2865,7 +2877,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2879,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2890,10 +2902,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2907,7 +2919,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2921,7 +2933,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2935,7 +2947,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2949,7 +2961,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2963,7 +2975,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2977,7 +2989,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2988,10 +3000,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3005,7 +3017,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3019,7 +3031,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3033,7 +3045,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3047,7 +3059,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,10 +3070,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3075,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3089,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3103,7 +3115,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3117,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3131,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3145,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3159,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3173,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3187,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3201,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3215,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3229,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3243,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3257,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3271,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3285,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3299,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3313,7 +3325,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3324,10 +3336,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,10 +3350,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3355,7 +3367,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3369,7 +3381,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3383,7 +3395,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3397,7 +3409,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3411,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3425,7 +3437,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3439,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3450,10 +3462,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,10 +3476,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3481,7 +3493,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,10 +3504,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3509,7 +3521,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3523,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3537,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3551,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3565,7 +3577,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3579,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3593,7 +3605,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3604,10 +3616,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3621,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3635,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3649,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3663,7 +3675,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3677,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3691,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>269</v>
+        <v>325</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3705,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3719,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3733,7 +3745,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3747,7 +3759,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3761,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3775,7 +3787,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3789,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,7 +3815,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3817,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3831,7 +3843,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3845,7 +3857,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3859,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3873,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3887,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3901,7 +3913,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3915,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3929,7 +3941,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3943,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3957,7 +3969,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3971,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3985,7 +3997,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3999,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4013,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4027,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4041,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>377</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4055,7 +4067,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4069,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4083,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,10 +4106,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4111,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4125,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4139,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4153,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>406</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4167,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4181,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4195,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4209,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>407</v>
+        <v>273</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4223,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4237,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4251,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4265,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4279,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4293,7 +4305,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4307,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4321,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4335,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4349,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4363,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4377,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4391,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4405,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4419,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4433,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4447,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4461,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4475,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4489,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4503,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4517,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,10 +4540,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4545,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4573,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4587,7 +4599,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,7 +4613,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4615,7 +4627,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4629,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4640,10 +4652,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,10 +4666,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4685,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4699,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4710,10 +4722,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4727,7 +4739,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4741,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4755,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4769,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4783,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4797,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4811,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4825,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4839,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4853,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>452</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4867,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4881,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4895,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>268</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4909,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4923,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4937,7 +4949,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4951,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4965,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4979,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,10 +5002,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5007,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5021,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5035,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5049,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5063,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5074,10 +5086,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5091,7 +5103,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5105,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5119,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5133,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>349</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5147,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5161,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>469</v>
+        <v>420</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5175,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>470</v>
+        <v>381</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5189,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5203,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5217,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>472</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5231,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5245,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5259,7 +5271,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5273,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5287,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5301,7 +5313,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5315,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5329,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5343,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5357,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5371,7 +5383,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5385,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>337</v>
+        <v>488</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5399,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>484</v>
+        <v>394</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5413,7 +5425,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
